--- a/BaseTraining/unit12_Uboot/unit12_Uboot.xlsx
+++ b/BaseTraining/unit12_Uboot/unit12_Uboot.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975110F8-0427-4F7A-BD63-E31B08697ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="184">
   <si>
     <t>protocall driver cho nokia 5110</t>
   </si>
@@ -578,7 +577,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -589,7 +588,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -744,7 +743,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -762,7 +761,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -777,7 +776,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -792,7 +791,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -818,7 +817,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -833,7 +832,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -851,7 +850,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -887,7 +886,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -898,7 +897,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -922,7 +921,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -933,7 +932,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -948,7 +947,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="163"/>
         <scheme val="minor"/>
@@ -959,7 +958,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -982,23 +981,233 @@
       <t>include/configs/omap3_beagle.h</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">🧩 Vai trò của </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>U_BOOT_CMD</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> trong autoboot</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">    bootm, CONFIG_SYS_MAXARGS, 1, do_bootm,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "Boot application image from memory",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "Usage: bootm &lt;addr&gt;"</t>
+  </si>
+  <si>
+    <t>);</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">➡️ Nếu lệnh không được đăng ký bằng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>U_BOOT_CMD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, thì khi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>bootcmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> gọi nó, U-Boot sẽ báo lỗi “Unknown command”.</t>
+    </r>
+  </si>
+  <si>
+    <t>✅ 2. Tạo bảng lệnh (command table)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Macro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>U_BOOT_CMD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tạo ra một entry kiểu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>cmd_tbl_t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> và đặt nó vào một section đặc biệt trong bộ nhớ.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Khi U-Boot khởi động, nó quét các entry này để xây dựng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>bảng lệnh nội bộ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Khi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>autoboot_command()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> gọi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>run_command_list(getenv("bootcmd"))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, nó tra bảng này để thực thi từng lệnh.</t>
+    </r>
+  </si>
+  <si>
+    <t>Đăng ký chuỗi cmd U_BOOT_CMD</t>
+  </si>
+  <si>
+    <t>VD:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">✅ 1. Đăng ký các lệnh mà </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>bootcmd</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> sẽ gọi</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1006,7 +1215,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1056,7 +1265,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -1064,14 +1273,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="9"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1079,7 +1288,7 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -1087,7 +1296,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -1096,7 +1305,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -1105,21 +1314,21 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF002060"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1128,8 +1337,36 @@
       <color rgb="FF00B0F0"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1163,6 +1400,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1333,7 +1576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1445,6 +1688,18 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5024,6 +5279,161 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="Shape 7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2000250" y="18135600"/>
+          <a:ext cx="1095375" cy="238125"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -138753"/>
+            <a:gd name="adj2" fmla="val 102099"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465A4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" strike="noStrike" spc="-1">
+              <a:latin typeface="Times New Roman"/>
+            </a:rPr>
+            <a:t>Command</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" strike="noStrike" spc="-1" baseline="0">
+              <a:latin typeface="Times New Roman"/>
+            </a:rPr>
+            <a:t> name</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1200" b="0" strike="noStrike" spc="-1">
+            <a:latin typeface="Times New Roman"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>133349</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>199919</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="Shape 7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3333749" y="18164175"/>
+          <a:ext cx="1866795" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -58308"/>
+            <a:gd name="adj2" fmla="val 91100"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465A4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" strike="noStrike" spc="-1">
+              <a:latin typeface="Times New Roman"/>
+            </a:rPr>
+            <a:t>Command execution function</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6177,9 +6587,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E11"/>
-  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="3.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" t="s">
@@ -6237,9 +6647,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BZ64"/>
-  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="3.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:57">
       <c r="B1" t="s">
@@ -6308,12 +6718,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:57" ht="14.4" thickBot="1">
+    <row r="7" spans="1:57" ht="15.75" thickBot="1">
       <c r="B7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:57" s="27" customFormat="1" ht="14.4" thickBot="1">
+    <row r="8" spans="1:57" s="27" customFormat="1" ht="15.75" thickBot="1">
       <c r="A8" s="26"/>
       <c r="C8" s="28"/>
       <c r="D8" s="28"/>
@@ -6321,8 +6731,8 @@
       <c r="F8" s="28"/>
       <c r="G8" s="28"/>
     </row>
-    <row r="9" spans="1:57" ht="14.4" thickBot="1"/>
-    <row r="10" spans="1:57" ht="14.4" thickBot="1">
+    <row r="9" spans="1:57" ht="15.75" thickBot="1"/>
+    <row r="10" spans="1:57" ht="15.75" thickBot="1">
       <c r="B10" s="29" t="s">
         <v>26</v>
       </c>
@@ -6412,11 +6822,11 @@
       <c r="BD16" s="34"/>
       <c r="BE16" s="35"/>
     </row>
-    <row r="17" spans="1:53" ht="14.4" thickBot="1"/>
-    <row r="18" spans="1:53" s="27" customFormat="1" ht="14.4" thickBot="1">
+    <row r="17" spans="1:53" ht="15.75" thickBot="1"/>
+    <row r="18" spans="1:53" s="27" customFormat="1" ht="15.75" thickBot="1">
       <c r="A18" s="26"/>
     </row>
-    <row r="19" spans="1:53" ht="16.8">
+    <row r="19" spans="1:53" ht="16.5">
       <c r="C19" s="24" t="s">
         <v>24</v>
       </c>
@@ -6425,7 +6835,7 @@
       <c r="F19" s="24"/>
       <c r="G19" s="24"/>
     </row>
-    <row r="20" spans="1:53" ht="20.399999999999999">
+    <row r="20" spans="1:53" ht="21">
       <c r="C20" s="19" t="s">
         <v>12</v>
       </c>
@@ -6434,7 +6844,7 @@
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
     </row>
-    <row r="21" spans="1:53" ht="16.8">
+    <row r="21" spans="1:53" ht="16.5">
       <c r="H21" s="20" t="s">
         <v>13</v>
       </c>
@@ -6444,7 +6854,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:53" ht="16.8">
+    <row r="23" spans="1:53" ht="16.5">
       <c r="H23" s="20" t="s">
         <v>25</v>
       </c>
@@ -6473,7 +6883,7 @@
       <c r="F24" s="17"/>
       <c r="G24" s="17"/>
     </row>
-    <row r="25" spans="1:53" ht="20.399999999999999">
+    <row r="25" spans="1:53" ht="21">
       <c r="C25" s="19" t="s">
         <v>15</v>
       </c>
@@ -6482,7 +6892,7 @@
       <c r="F25" s="19"/>
       <c r="G25" s="19"/>
     </row>
-    <row r="26" spans="1:53" ht="16.8">
+    <row r="26" spans="1:53" ht="16.5">
       <c r="C26" s="20" t="s">
         <v>16</v>
       </c>
@@ -6491,7 +6901,7 @@
       <c r="F26" s="20"/>
       <c r="G26" s="20"/>
     </row>
-    <row r="27" spans="1:53" ht="16.8">
+    <row r="27" spans="1:53" ht="16.5">
       <c r="C27" s="20" t="s">
         <v>17</v>
       </c>
@@ -6500,7 +6910,7 @@
       <c r="F27" s="20"/>
       <c r="G27" s="20"/>
     </row>
-    <row r="28" spans="1:53" ht="16.8">
+    <row r="28" spans="1:53" ht="16.5">
       <c r="C28" s="22" t="s">
         <v>18</v>
       </c>
@@ -6509,7 +6919,7 @@
       <c r="F28" s="22"/>
       <c r="G28" s="22"/>
     </row>
-    <row r="29" spans="1:53" ht="16.8">
+    <row r="29" spans="1:53" ht="16.5">
       <c r="C29" s="23" t="s">
         <v>19</v>
       </c>
@@ -6518,7 +6928,7 @@
       <c r="F29" s="23"/>
       <c r="G29" s="23"/>
     </row>
-    <row r="30" spans="1:53" ht="16.8">
+    <row r="30" spans="1:53" ht="16.5">
       <c r="C30" s="23" t="s">
         <v>20</v>
       </c>
@@ -6527,7 +6937,7 @@
       <c r="F30" s="23"/>
       <c r="G30" s="23"/>
     </row>
-    <row r="31" spans="1:53" ht="16.8">
+    <row r="31" spans="1:53" ht="16.5">
       <c r="C31" s="23" t="s">
         <v>21</v>
       </c>
@@ -6543,7 +6953,7 @@
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
     </row>
-    <row r="33" spans="2:64" ht="20.399999999999999">
+    <row r="33" spans="2:64" ht="21">
       <c r="C33" s="19" t="s">
         <v>22</v>
       </c>
@@ -6552,7 +6962,7 @@
       <c r="F33" s="19"/>
       <c r="G33" s="19"/>
     </row>
-    <row r="34" spans="2:64" ht="16.8">
+    <row r="34" spans="2:64" ht="16.5">
       <c r="C34" s="18" t="s">
         <v>23</v>
       </c>
@@ -6562,51 +6972,51 @@
       <c r="G34" s="18"/>
     </row>
     <row r="36" spans="2:64">
-      <c r="N36" s="82" t="s">
+      <c r="N36" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="O36" s="83"/>
-      <c r="P36" s="83"/>
-      <c r="Q36" s="83"/>
-      <c r="R36" s="83"/>
-      <c r="S36" s="83"/>
-      <c r="T36" s="83"/>
-      <c r="U36" s="83"/>
-      <c r="V36" s="83"/>
-      <c r="W36" s="84"/>
-      <c r="Z36" s="82" t="s">
+      <c r="O36" s="89"/>
+      <c r="P36" s="89"/>
+      <c r="Q36" s="89"/>
+      <c r="R36" s="89"/>
+      <c r="S36" s="89"/>
+      <c r="T36" s="89"/>
+      <c r="U36" s="89"/>
+      <c r="V36" s="89"/>
+      <c r="W36" s="90"/>
+      <c r="Z36" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="AA36" s="83"/>
-      <c r="AB36" s="83"/>
-      <c r="AC36" s="83"/>
-      <c r="AD36" s="83"/>
-      <c r="AE36" s="83"/>
-      <c r="AF36" s="83"/>
-      <c r="AG36" s="84"/>
-      <c r="AO36" s="82" t="s">
+      <c r="AA36" s="89"/>
+      <c r="AB36" s="89"/>
+      <c r="AC36" s="89"/>
+      <c r="AD36" s="89"/>
+      <c r="AE36" s="89"/>
+      <c r="AF36" s="89"/>
+      <c r="AG36" s="90"/>
+      <c r="AO36" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="AP36" s="83"/>
-      <c r="AQ36" s="83"/>
-      <c r="AR36" s="83"/>
-      <c r="AS36" s="83"/>
-      <c r="AT36" s="83"/>
-      <c r="AU36" s="83"/>
-      <c r="AV36" s="83"/>
-      <c r="AW36" s="83"/>
-      <c r="AX36" s="83"/>
-      <c r="AY36" s="83"/>
-      <c r="AZ36" s="83"/>
-      <c r="BA36" s="84"/>
-      <c r="BG36" s="82" t="s">
+      <c r="AP36" s="89"/>
+      <c r="AQ36" s="89"/>
+      <c r="AR36" s="89"/>
+      <c r="AS36" s="89"/>
+      <c r="AT36" s="89"/>
+      <c r="AU36" s="89"/>
+      <c r="AV36" s="89"/>
+      <c r="AW36" s="89"/>
+      <c r="AX36" s="89"/>
+      <c r="AY36" s="89"/>
+      <c r="AZ36" s="89"/>
+      <c r="BA36" s="90"/>
+      <c r="BG36" s="88" t="s">
         <v>52</v>
       </c>
-      <c r="BH36" s="83"/>
-      <c r="BI36" s="83"/>
-      <c r="BJ36" s="83"/>
-      <c r="BK36" s="83"/>
-      <c r="BL36" s="84"/>
+      <c r="BH36" s="89"/>
+      <c r="BI36" s="89"/>
+      <c r="BJ36" s="89"/>
+      <c r="BK36" s="89"/>
+      <c r="BL36" s="90"/>
     </row>
     <row r="37" spans="2:64">
       <c r="R37" s="6"/>
@@ -6898,12 +7308,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CJ81"/>
-  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="3.140625" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:83" ht="14.4" thickBot="1"/>
-    <row r="2" spans="1:83" ht="14.4" thickBot="1">
+    <row r="1" spans="1:83" ht="15.75" thickBot="1"/>
+    <row r="2" spans="1:83" ht="15.75" thickBot="1">
       <c r="B2" s="29" t="s">
         <v>26</v>
       </c>
@@ -6987,74 +7397,74 @@
       <c r="AY8" s="34"/>
       <c r="AZ8" s="35"/>
     </row>
-    <row r="9" spans="1:83" ht="14.4" thickBot="1"/>
-    <row r="10" spans="1:83" s="27" customFormat="1" ht="14.4" thickBot="1">
+    <row r="9" spans="1:83" ht="15.75" thickBot="1"/>
+    <row r="10" spans="1:83" s="27" customFormat="1" ht="15.75" thickBot="1">
       <c r="A10" s="26"/>
     </row>
     <row r="13" spans="1:83">
-      <c r="K13" s="82" t="s">
+      <c r="K13" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="L13" s="83"/>
-      <c r="M13" s="83"/>
-      <c r="N13" s="83"/>
-      <c r="O13" s="83"/>
-      <c r="P13" s="83"/>
-      <c r="Q13" s="83"/>
-      <c r="R13" s="83"/>
-      <c r="S13" s="83"/>
-      <c r="T13" s="84"/>
-      <c r="W13" s="82" t="s">
+      <c r="L13" s="89"/>
+      <c r="M13" s="89"/>
+      <c r="N13" s="89"/>
+      <c r="O13" s="89"/>
+      <c r="P13" s="89"/>
+      <c r="Q13" s="89"/>
+      <c r="R13" s="89"/>
+      <c r="S13" s="89"/>
+      <c r="T13" s="90"/>
+      <c r="W13" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="X13" s="83"/>
-      <c r="Y13" s="83"/>
-      <c r="Z13" s="83"/>
-      <c r="AA13" s="83"/>
-      <c r="AB13" s="83"/>
-      <c r="AC13" s="83"/>
-      <c r="AD13" s="84"/>
+      <c r="X13" s="89"/>
+      <c r="Y13" s="89"/>
+      <c r="Z13" s="89"/>
+      <c r="AA13" s="89"/>
+      <c r="AB13" s="89"/>
+      <c r="AC13" s="89"/>
+      <c r="AD13" s="90"/>
       <c r="AJ13" s="6"/>
-      <c r="AK13" s="82" t="s">
+      <c r="AK13" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="AL13" s="83"/>
-      <c r="AM13" s="83"/>
-      <c r="AN13" s="83"/>
-      <c r="AO13" s="83"/>
-      <c r="AP13" s="84"/>
-      <c r="AW13" s="82" t="s">
+      <c r="AL13" s="89"/>
+      <c r="AM13" s="89"/>
+      <c r="AN13" s="89"/>
+      <c r="AO13" s="89"/>
+      <c r="AP13" s="90"/>
+      <c r="AW13" s="88" t="s">
         <v>64</v>
       </c>
-      <c r="AX13" s="83"/>
-      <c r="AY13" s="83"/>
-      <c r="AZ13" s="83"/>
-      <c r="BA13" s="83"/>
-      <c r="BB13" s="84"/>
-      <c r="BH13" s="82" t="s">
+      <c r="AX13" s="89"/>
+      <c r="AY13" s="89"/>
+      <c r="AZ13" s="89"/>
+      <c r="BA13" s="89"/>
+      <c r="BB13" s="90"/>
+      <c r="BH13" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="BI13" s="83"/>
-      <c r="BJ13" s="83"/>
-      <c r="BK13" s="83"/>
-      <c r="BL13" s="83"/>
-      <c r="BM13" s="84"/>
-      <c r="BR13" s="82" t="s">
+      <c r="BI13" s="89"/>
+      <c r="BJ13" s="89"/>
+      <c r="BK13" s="89"/>
+      <c r="BL13" s="89"/>
+      <c r="BM13" s="90"/>
+      <c r="BR13" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="BS13" s="83"/>
-      <c r="BT13" s="83"/>
-      <c r="BU13" s="83"/>
-      <c r="BV13" s="83"/>
-      <c r="BW13" s="84"/>
-      <c r="BZ13" s="82" t="s">
+      <c r="BS13" s="89"/>
+      <c r="BT13" s="89"/>
+      <c r="BU13" s="89"/>
+      <c r="BV13" s="89"/>
+      <c r="BW13" s="90"/>
+      <c r="BZ13" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="CA13" s="83"/>
-      <c r="CB13" s="83"/>
-      <c r="CC13" s="83"/>
-      <c r="CD13" s="83"/>
-      <c r="CE13" s="84"/>
+      <c r="CA13" s="89"/>
+      <c r="CB13" s="89"/>
+      <c r="CC13" s="89"/>
+      <c r="CD13" s="89"/>
+      <c r="CE13" s="90"/>
     </row>
     <row r="14" spans="1:83">
       <c r="O14" s="6"/>
@@ -8649,9 +9059,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88332979-A2FD-4E58-B6E8-B4E152EFAC60}">
-  <dimension ref="B20:BM96"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="13.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A20:BM114"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="15"/>
   <sheetData>
     <row r="20" spans="2:15">
       <c r="B20" s="52" t="s">
@@ -8809,28 +9219,28 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="2:44" ht="17.399999999999999">
+    <row r="34" spans="2:44" ht="18.75">
       <c r="B34" s="59" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="37" spans="2:44">
-      <c r="F37" s="82" t="s">
+      <c r="F37" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="G37" s="83"/>
-      <c r="H37" s="83"/>
-      <c r="I37" s="83"/>
-      <c r="J37" s="83"/>
-      <c r="K37" s="84"/>
-      <c r="N37" s="82" t="s">
+      <c r="G37" s="89"/>
+      <c r="H37" s="89"/>
+      <c r="I37" s="89"/>
+      <c r="J37" s="89"/>
+      <c r="K37" s="90"/>
+      <c r="N37" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="O37" s="83"/>
-      <c r="P37" s="83"/>
-      <c r="Q37" s="83"/>
-      <c r="R37" s="83"/>
-      <c r="S37" s="84"/>
+      <c r="O37" s="89"/>
+      <c r="P37" s="89"/>
+      <c r="Q37" s="89"/>
+      <c r="R37" s="89"/>
+      <c r="S37" s="90"/>
       <c r="Y37" s="10"/>
       <c r="Z37" s="11" t="s">
         <v>102</v>
@@ -9243,7 +9653,7 @@
       <c r="AS71" s="11"/>
       <c r="AT71" s="12"/>
     </row>
-    <row r="72" spans="8:65" ht="14.4" thickBot="1">
+    <row r="72" spans="8:65" ht="15.75" thickBot="1">
       <c r="H72" s="6"/>
       <c r="I72" s="5"/>
       <c r="J72" s="6"/>
@@ -9255,7 +9665,7 @@
       <c r="AQ72" s="2"/>
       <c r="AR72" s="4"/>
     </row>
-    <row r="73" spans="8:65" ht="14.4" thickBot="1">
+    <row r="73" spans="8:65" ht="15.75" thickBot="1">
       <c r="H73" s="6"/>
       <c r="I73" s="5"/>
       <c r="J73" s="6"/>
@@ -9365,7 +9775,7 @@
       <c r="AS80" s="11"/>
       <c r="AT80" s="12"/>
     </row>
-    <row r="81" spans="8:44">
+    <row r="81" spans="1:44">
       <c r="H81" s="6"/>
       <c r="I81" s="5"/>
       <c r="J81" s="6"/>
@@ -9377,7 +9787,7 @@
       <c r="AQ81" s="2"/>
       <c r="AR81" s="4"/>
     </row>
-    <row r="82" spans="8:44">
+    <row r="82" spans="1:44">
       <c r="H82" s="6"/>
       <c r="I82" s="5"/>
       <c r="J82" s="6"/>
@@ -9391,7 +9801,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="83" spans="8:44">
+    <row r="83" spans="1:44">
       <c r="H83" s="6"/>
       <c r="I83" s="5"/>
       <c r="J83" s="6"/>
@@ -9403,7 +9813,7 @@
       <c r="AQ83" s="7"/>
       <c r="AR83" s="9"/>
     </row>
-    <row r="84" spans="8:44">
+    <row r="84" spans="1:44">
       <c r="H84" s="6"/>
       <c r="I84" s="5"/>
       <c r="J84" s="6"/>
@@ -9413,7 +9823,7 @@
       <c r="AA84" s="6"/>
       <c r="AP84" s="6"/>
     </row>
-    <row r="85" spans="8:44">
+    <row r="85" spans="1:44">
       <c r="H85" s="6"/>
       <c r="I85" s="7"/>
       <c r="J85" s="9"/>
@@ -9421,19 +9831,19 @@
       <c r="AA85" s="6"/>
       <c r="AP85" s="6"/>
     </row>
-    <row r="86" spans="8:44">
+    <row r="86" spans="1:44">
       <c r="H86" s="6"/>
       <c r="P86" s="6"/>
       <c r="AA86" s="6"/>
       <c r="AP86" s="6"/>
     </row>
-    <row r="87" spans="8:44">
+    <row r="87" spans="1:44">
       <c r="H87" s="6"/>
       <c r="P87" s="6"/>
       <c r="AA87" s="6"/>
       <c r="AP87" s="6"/>
     </row>
-    <row r="88" spans="8:44">
+    <row r="88" spans="1:44">
       <c r="H88" s="6"/>
       <c r="P88" s="6"/>
       <c r="V88" t="s">
@@ -9442,53 +9852,105 @@
       <c r="AA88" s="6"/>
       <c r="AP88" s="6"/>
     </row>
-    <row r="89" spans="8:44">
-      <c r="H89" s="6"/>
-      <c r="P89" s="6"/>
-      <c r="AA89" s="6"/>
-      <c r="AP89" s="6"/>
-    </row>
-    <row r="90" spans="8:44">
-      <c r="H90" s="6"/>
-      <c r="P90" s="6"/>
-      <c r="AA90" s="6"/>
-      <c r="AP90" s="6"/>
-    </row>
-    <row r="91" spans="8:44">
-      <c r="H91" s="6"/>
-      <c r="P91" s="6"/>
-      <c r="AA91" s="6"/>
-      <c r="AP91" s="6"/>
-    </row>
-    <row r="92" spans="8:44">
-      <c r="H92" s="6"/>
-      <c r="P92" s="6"/>
-      <c r="AA92" s="6"/>
-      <c r="AP92" s="6"/>
-    </row>
-    <row r="93" spans="8:44">
-      <c r="H93" s="6"/>
-      <c r="P93" s="6"/>
-      <c r="AA93" s="6"/>
-      <c r="AP93" s="6"/>
-    </row>
-    <row r="94" spans="8:44">
-      <c r="H94" s="6"/>
-      <c r="P94" s="6"/>
-      <c r="AA94" s="6"/>
-      <c r="AP94" s="6"/>
-    </row>
-    <row r="95" spans="8:44">
-      <c r="H95" s="6"/>
-      <c r="P95" s="6"/>
-      <c r="AA95" s="6"/>
-      <c r="AP95" s="6"/>
-    </row>
-    <row r="96" spans="8:44">
-      <c r="H96" s="6"/>
-      <c r="P96" s="6"/>
-      <c r="AA96" s="6"/>
-      <c r="AP96" s="6"/>
+    <row r="89" spans="1:44" ht="15.75" thickBot="1"/>
+    <row r="90" spans="1:44" s="83" customFormat="1" ht="21.75" thickBot="1">
+      <c r="A90" s="82"/>
+      <c r="B90" s="84" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="92" spans="1:44" ht="26.25">
+      <c r="B92" s="85" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="93" spans="1:44" ht="21">
+      <c r="B93" s="87" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="94" spans="1:44">
+      <c r="B94" s="17"/>
+      <c r="C94" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="95" spans="1:44">
+      <c r="D95" s="21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="96" spans="1:44">
+      <c r="D96" s="21" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4">
+      <c r="D97" s="21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4">
+      <c r="D98" s="21" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4">
+      <c r="D99" s="21" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4" ht="16.5">
+      <c r="B100" s="18" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4">
+      <c r="B101" s="17"/>
+    </row>
+    <row r="102" spans="2:4" ht="21">
+      <c r="B102" s="87" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4" ht="16.5">
+      <c r="B103" s="20" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4" ht="16.5">
+      <c r="B104" s="20" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4" ht="16.5">
+      <c r="B105" s="20" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4">
+      <c r="B106" s="17"/>
+    </row>
+    <row r="107" spans="2:4" ht="21">
+      <c r="B107" s="19"/>
+    </row>
+    <row r="108" spans="2:4">
+      <c r="B108" s="22"/>
+    </row>
+    <row r="109" spans="2:4" ht="16.5">
+      <c r="B109" s="20"/>
+    </row>
+    <row r="110" spans="2:4">
+      <c r="B110" s="86"/>
+    </row>
+    <row r="111" spans="2:4">
+      <c r="B111" s="86"/>
+    </row>
+    <row r="112" spans="2:4">
+      <c r="B112" s="86"/>
+    </row>
+    <row r="114" spans="2:2">
+      <c r="B114" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9496,16 +9958,17 @@
     <mergeCell ref="N37:S37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B97659E-0B8C-451B-B9D6-7BDEA7E84F0C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:AY57"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:51" ht="22.8">
+    <row r="2" spans="1:51" ht="23.25">
       <c r="B2" s="68" t="s">
         <v>139</v>
       </c>
@@ -9688,15 +10151,15 @@
         <v>155</v>
       </c>
     </row>
-    <row r="13" spans="1:51" ht="14.4" thickBot="1"/>
-    <row r="14" spans="1:51" s="65" customFormat="1" ht="14.4" thickBot="1">
+    <row r="13" spans="1:51" ht="15.75" thickBot="1"/>
+    <row r="14" spans="1:51" s="65" customFormat="1" ht="15.75" thickBot="1">
       <c r="A14" s="74"/>
       <c r="B14" s="75" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="15" spans="1:51" ht="14.4" thickBot="1"/>
-    <row r="16" spans="1:51" ht="14.4" thickBot="1">
+    <row r="15" spans="1:51" ht="15.75" thickBot="1"/>
+    <row r="16" spans="1:51" ht="15.75" thickBot="1">
       <c r="C16" s="76" t="s">
         <v>157</v>
       </c>
@@ -9722,20 +10185,20 @@
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="12"/>
-      <c r="P18" s="82" t="s">
+      <c r="P18" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="Q18" s="83"/>
-      <c r="R18" s="83"/>
-      <c r="S18" s="83"/>
-      <c r="T18" s="83"/>
-      <c r="U18" s="84"/>
-      <c r="X18" s="82" t="s">
+      <c r="Q18" s="89"/>
+      <c r="R18" s="89"/>
+      <c r="S18" s="89"/>
+      <c r="T18" s="89"/>
+      <c r="U18" s="90"/>
+      <c r="X18" s="88" t="s">
         <v>161</v>
       </c>
-      <c r="Y18" s="83"/>
-      <c r="Z18" s="83"/>
-      <c r="AA18" s="84"/>
+      <c r="Y18" s="89"/>
+      <c r="Z18" s="89"/>
+      <c r="AA18" s="90"/>
     </row>
     <row r="19" spans="4:29">
       <c r="F19" s="4"/>
@@ -10121,9 +10584,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D37D8AE1-203C-42DF-8D3A-6A86DDA0335D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="C2:C17"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="3:3">
       <c r="C2" t="s">
